--- a/taskOneChild.xlsx
+++ b/taskOneChild.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
   <si>
     <t>XOR.id</t>
   </si>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>402881c3560c2f7c01560c2f83a60009</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
@@ -701,7 +707,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7.1640625" customWidth="1"/>
@@ -710,17 +716,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
     </row>

--- a/taskOneChild.xlsx
+++ b/taskOneChild.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="26722"/>
   <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="440" windowWidth="25600" windowHeight="15620" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="440" windowWidth="25600" windowHeight="15620" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
   <si>
     <t>XOR.id</t>
   </si>
@@ -42,9 +42,6 @@
     <t>scheduledFinish</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>isCriticalSystemObject</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>402881c3560c2f7c01560c2f83a6000a</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>17b219b1-aa16-4bf8-a33a-af24f4328c3f</t>
   </si>
   <si>
-    <t>402881c3560c2f7c01560c2f83a7000b</t>
-  </si>
-  <si>
     <t>This is the first child task</t>
   </si>
   <si>
@@ -172,9 +163,6 @@
   </si>
   <si>
     <t>tools.xor.db.pm.TaskDetails</t>
-  </si>
-  <si>
-    <t>402881c3560c2f7c01560c2f83a60009</t>
   </si>
   <si>
     <t>a</t>
@@ -549,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="38.1640625" customWidth="1"/>
@@ -558,29 +546,28 @@
     <col min="4" max="4" width="18.5" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
     <col min="6" max="6" width="15.1640625" customWidth="1"/>
-    <col min="7" max="7" width="34.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.5" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="54" customWidth="1"/>
-    <col min="12" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" customWidth="1"/>
-    <col min="17" max="17" width="43.1640625" customWidth="1"/>
-    <col min="18" max="18" width="12.5" customWidth="1"/>
-    <col min="19" max="19" width="17.33203125" customWidth="1"/>
-    <col min="20" max="20" width="15.5" customWidth="1"/>
-    <col min="21" max="21" width="18.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.83203125" customWidth="1"/>
-    <col min="24" max="25" width="16.1640625" customWidth="1"/>
-    <col min="26" max="26" width="16.33203125" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" customWidth="1"/>
-    <col min="28" max="28" width="15" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="54" customWidth="1"/>
+    <col min="11" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" customWidth="1"/>
+    <col min="16" max="16" width="43.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" customWidth="1"/>
+    <col min="19" max="19" width="15.5" customWidth="1"/>
+    <col min="20" max="20" width="18.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="24" width="16.1640625" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" customWidth="1"/>
+    <col min="27" max="27" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -662,37 +649,31 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" t="s">
+      <c r="Q2" t="s">
         <v>34</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -716,26 +697,26 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +731,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="38.1640625" customWidth="1"/>
@@ -760,33 +741,32 @@
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="7.5" customWidth="1"/>
     <col min="7" max="7" width="15.1640625" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.5" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="7.6640625" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="12.5" customWidth="1"/>
-    <col min="20" max="20" width="17.33203125" customWidth="1"/>
-    <col min="21" max="21" width="15.5" customWidth="1"/>
-    <col min="22" max="22" width="18.6640625" customWidth="1"/>
-    <col min="23" max="23" width="38.1640625" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" customWidth="1"/>
-    <col min="25" max="25" width="37.5" customWidth="1"/>
-    <col min="26" max="26" width="16.1640625" customWidth="1"/>
-    <col min="27" max="27" width="16.33203125" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" customWidth="1"/>
-    <col min="29" max="29" width="15" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" customWidth="1"/>
+    <col min="20" max="20" width="15.5" customWidth="1"/>
+    <col min="21" max="21" width="18.6640625" customWidth="1"/>
+    <col min="22" max="22" width="38.1640625" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="37.5" customWidth="1"/>
+    <col min="25" max="25" width="16.1640625" customWidth="1"/>
+    <col min="26" max="26" width="16.33203125" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" customWidth="1"/>
+    <col min="28" max="28" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -869,43 +849,37 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="V2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" t="s">
         <v>44</v>
-      </c>
-      <c r="M2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>46</v>
-      </c>
-      <c r="W2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -920,24 +894,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="37.5" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="7.5" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" customWidth="1"/>
-    <col min="9" max="9" width="37" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="37" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -946,45 +919,39 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
